--- a/tests/fixtures/sample_pattern_native_roadmap.xlsx
+++ b/tests/fixtures/sample_pattern_native_roadmap.xlsx
@@ -418,120 +418,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="B1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>SEO Retainer Breakdown</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Client:</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Sample Retail Co</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+    <row r="5">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Month 1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Month 2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Month 3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Month 4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Month 5</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Month 6</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Month 7</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Month 8</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Month 9</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Month 10</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Month 11</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Month 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Monthly Retainer</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Consulting Hours</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G6" t="n">
         <v>8</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H6" t="n">
         <v>8</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I6" t="n">
         <v>8</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J6" t="n">
         <v>8</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K6" t="n">
         <v>8</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L6" t="n">
         <v>8</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M6" t="n">
         <v>8</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N6" t="n">
         <v>8</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O6" t="n">
         <v>8</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P6" t="n">
         <v>8</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q6" t="n">
         <v>8</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R6" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="6">
-      <c r="E6" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hours P/M</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>24</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Technical Hours</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="G7" t="n">
         <v>12</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" t="n">
         <v>12</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>12</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>12</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>12</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L7" t="n">
         <v>12</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M7" t="n">
         <v>12</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N7" t="n">
         <v>12</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O7" t="n">
         <v>12</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P7" t="n">
         <v>12</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q7" t="n">
         <v>12</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R7" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cost P/H</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>200</v>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Content Hours</t>
@@ -574,47 +643,176 @@
         <v>20</v>
       </c>
     </row>
+    <row r="9">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Link Hours</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6</v>
+      </c>
+    </row>
     <row r="10">
       <c r="E10" t="inlineStr">
         <is>
-          <t>Link Hours</t>
+          <t>Hours Allocated</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="O10" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="R10" t="n">
-        <v>6</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Hours to Use</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>24</v>
+      </c>
+      <c r="H11" t="n">
+        <v>24</v>
+      </c>
+      <c r="I11" t="n">
+        <v>24</v>
+      </c>
+      <c r="J11" t="n">
+        <v>24</v>
+      </c>
+      <c r="K11" t="n">
+        <v>24</v>
+      </c>
+      <c r="L11" t="n">
+        <v>24</v>
+      </c>
+      <c r="M11" t="n">
+        <v>24</v>
+      </c>
+      <c r="N11" t="n">
+        <v>24</v>
+      </c>
+      <c r="O11" t="n">
+        <v>24</v>
+      </c>
+      <c r="P11" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>24</v>
+      </c>
+      <c r="R11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>% of Retainer</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>100</v>
+      </c>
+      <c r="H12" t="n">
+        <v>100</v>
+      </c>
+      <c r="I12" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" t="n">
+        <v>100</v>
+      </c>
+      <c r="K12" t="n">
+        <v>100</v>
+      </c>
+      <c r="L12" t="n">
+        <v>100</v>
+      </c>
+      <c r="M12" t="n">
+        <v>100</v>
+      </c>
+      <c r="N12" t="n">
+        <v>100</v>
+      </c>
+      <c r="O12" t="n">
+        <v>100</v>
+      </c>
+      <c r="P12" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>100</v>
+      </c>
+      <c r="R12" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -628,116 +826,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="B1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>SEO Retainer Agreement</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Client Name</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Sample Retail Co</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Fashion</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Monthly Retainer</t>
-        </is>
-      </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Project Start Date</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Monthly Retainer (excl tech fees)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>AUD 5000</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Project Start Date</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Main POC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>contact@sampleretail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pattern Client Partner</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>partner@pattern.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pattern SEO Lead</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>lead@pattern.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>CMS</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Primary Contact</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Jane Smith</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Account Manager</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>John Doe</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Contract Period</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>12 months</t>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Strategy Slides</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sample Retail Strategy 2026</t>
         </is>
       </c>
     </row>
@@ -752,129 +955,129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="B3:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="3">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Focus</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Occurrence</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Hours</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Cadence</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Monthly Strategy Review</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Monthly strategy direction call</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Keyword Research &amp; Mapping</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Keyword universe mapping</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
-      <c r="D3" t="n">
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Competitor Analysis</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Competitive landscape review</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GA4 &amp; GSC Reporting</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Monthly performance report and dashboard</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Content Gap Analysis</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Identify content opportunities</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Competitor Analysis</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>GA4 &amp; GSC Reporting</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Analytics</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Content Gap Analysis</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Bi-Annual</t>
         </is>
-      </c>
-      <c r="D6" t="n">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -888,129 +1091,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="B3:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="3">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Focus</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Occurrence</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Hours</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Cadence</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CMS:</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Core Web Vitals Audit</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CWV audit and fix recommendations</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Crawl Error Remediation</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fix crawl errors from GSC</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D3" t="n">
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Schema Markup Implementation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Product and breadcrumb schema</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Site Speed Optimisation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Image and script optimisation</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Schema Markup Implementation</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Site Speed Optimisation</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Internal Linking Audit</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Silo structure internal link review</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Bi-Annual</t>
         </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1024,52 +1239,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="B1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Content Production Plan</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>12-Month Schedule</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Month Name</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Content Name</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Focus</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Total Words</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1079,300 +1282,407 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Word Count</t>
+          <t>Keywords</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Content Brief Detail</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>FAQ Questions</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>SEO Hours</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Template set-up</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Production time</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>SEO Review Time</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>SEO Implementation time</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Month 1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Summer Fashion Guide 2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://example.com/blog/summer-fashion</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>New Page: Optimisation</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>summer fashion guide</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="N8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Month 1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>July</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>/blog/summer-fashion-guide</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Summer Fashion Guide 2026</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>New Page - Long Form</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>How to Style Denim FAQ</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://example.com/faq/how-to-style-denim</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>800</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Existing Copy: Optimisation &amp; FAQs</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>how to style denim</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Month 2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Spring Trends 2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://example.com/blog/spring-trends</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>New Page: Optimisation</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>spring fashion trends</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="L10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>July</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>/faq/how-to-style-denim</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>How to Style Denim - FAQ</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>FAQ Page</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>800</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="N10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Month 2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Women's Dresses Category</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://example.com/categories/womens-dresses</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>500</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Existing Copy: Optimisation</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>womens dresses</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>August</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>/blog/spring-trends</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Spring Trends 2026</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>New Page - Long Form</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1800</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="L11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Month 3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Workwear Essentials Guide</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://example.com/blog/workwear-essentials</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>New Page: Optimisation</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>workwear essentials</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Month 3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Classic Blazer Product Page</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://example.com/products/classic-blazer</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>400</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Existing Copy: Optimisation</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>classic blazer</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Month 4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Autumn Layering Techniques</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://example.com/blog/autumn-layering</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1900</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>New Page: Optimisation</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>autumn layering</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>August</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>/categories/womens-dresses</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Women's Dresses Category</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Optimisation</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>500</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>/blog/workwear-essentials</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Workwear Essentials Guide</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>New Page - Long Form</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I12" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>/products/classic-blazer</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Classic Blazer Product Page</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Optimisation</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>400</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="L14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>October</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>/blog/autumn-layering</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Autumn Layering Techniques</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>New Page - Long Form</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1900</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3</v>
+      <c r="N14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -1386,89 +1696,89 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="B3:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="3">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Focus</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Occurrence</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Hours</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Cadence</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Digital PR Outreach</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Off-Page</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pitch to lifestyle publications</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Guest Post Sourcing</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Off-Page</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Identify guest post opportunities</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Link Reclamation</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Off-Page</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Recover unlinked brand mentions</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
